--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_29-09-2025.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
